--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
@@ -6536,7 +6536,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260810_203307.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
